--- a/Result/profitability/2368.xlsx
+++ b/Result/profitability/2368.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>4.075</v>
+        <v>4.825</v>
       </c>
       <c r="N2" t="n">
-        <v>29.965</v>
+        <v>30.26</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6875</v>
+        <v>4.51875</v>
       </c>
       <c r="N3" t="n">
-        <v>27.88875</v>
+        <v>28.9775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4225</v>
+        <v>4.1325</v>
       </c>
       <c r="N4" t="n">
-        <v>26.9875</v>
+        <v>27.40625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>2.925</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>23.2175</v>
+        <v>23.85375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4675</v>
+        <v>2.81625</v>
       </c>
       <c r="N6" t="n">
-        <v>20.84</v>
+        <v>20.72625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>1.63625</v>
+        <v>2.05375</v>
       </c>
       <c r="N7" t="n">
-        <v>17.71375</v>
+        <v>17.8375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9025</v>
+        <v>1.20375</v>
       </c>
       <c r="N8" t="n">
-        <v>15.29625</v>
+        <v>15.27625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>24279</v>
+      </c>
+      <c r="D75" t="n">
+        <v>15866</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8413</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6418</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-118</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6299</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4783</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5.196250000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.22125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.409999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3508005822416302</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1600000000000037</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.004596380350474161</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1721921515561571</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
